--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.77906103386654</v>
+        <v>5.976597418003313</v>
       </c>
       <c r="D2" t="n">
-        <v>36.93327396648277</v>
+        <v>6.001657019553451</v>
       </c>
       <c r="E2" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F2" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.39134300892387</v>
+        <v>3.476093238950128</v>
       </c>
       <c r="D3" t="n">
-        <v>21.56870598937388</v>
+        <v>3.504914723273256</v>
       </c>
       <c r="E3" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F3" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>8.860293784778802</v>
+        <v>1.439797740026555</v>
       </c>
       <c r="D4" t="n">
-        <v>8.951863458979229</v>
+        <v>1.454677812084125</v>
       </c>
       <c r="E4" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F4" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.616389702883522</v>
+        <v>0.7501633267185723</v>
       </c>
       <c r="D5" t="n">
-        <v>4.878836854884864</v>
+        <v>0.7928109889187904</v>
       </c>
       <c r="E5" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F5" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.05261593159676</v>
+        <v>1.471050088884474</v>
       </c>
       <c r="D6" t="n">
-        <v>30.34697199103769</v>
+        <v>4.931382948543625</v>
       </c>
       <c r="E6" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F6" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.41529832586378</v>
+        <v>3.154985977952865</v>
       </c>
       <c r="D7" t="n">
-        <v>19.20348967462212</v>
+        <v>3.120567072126094</v>
       </c>
       <c r="E7" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F7" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.72545806087269</v>
+        <v>3.042886934891812</v>
       </c>
       <c r="D8" t="n">
-        <v>18.66004908273293</v>
+        <v>3.032257975944101</v>
       </c>
       <c r="E8" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F8" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.75774879739808</v>
+        <v>2.885634179577189</v>
       </c>
       <c r="D9" t="n">
-        <v>18.21655866208599</v>
+        <v>2.960190782588973</v>
       </c>
       <c r="E9" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F9" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.98703259966995</v>
+        <v>3.735392797446367</v>
       </c>
       <c r="D10" t="n">
-        <v>22.62792198673861</v>
+        <v>3.677037322845024</v>
       </c>
       <c r="E10" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F10" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51942620877534</v>
+        <v>5.284406758925994</v>
       </c>
       <c r="D11" t="n">
-        <v>30.67777224491963</v>
+        <v>4.98513798979944</v>
       </c>
       <c r="E11" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F11" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.01541990843153</v>
+        <v>4.552505735120124</v>
       </c>
       <c r="D12" t="n">
-        <v>28.18402756451147</v>
+        <v>4.579904479233114</v>
       </c>
       <c r="E12" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F12" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.54440265051239</v>
+        <v>6.263465430708264</v>
       </c>
       <c r="D13" t="n">
-        <v>36.32656577213481</v>
+        <v>5.903066937971907</v>
       </c>
       <c r="E13" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F13" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.59260215603949</v>
+        <v>4.158797850356418</v>
       </c>
       <c r="D14" t="n">
-        <v>23.36172558168234</v>
+        <v>3.796280407023381</v>
       </c>
       <c r="E14" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F14" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>12.50722380465629</v>
+        <v>2.032423868256648</v>
       </c>
       <c r="D15" t="n">
-        <v>9.973906705179928</v>
+        <v>1.620759839591738</v>
       </c>
       <c r="E15" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F15" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>16.60943696954843</v>
+        <v>2.69903350755162</v>
       </c>
       <c r="D16" t="n">
-        <v>16.62217033184619</v>
+        <v>2.701102678925006</v>
       </c>
       <c r="E16" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F16" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>52.47969949387424</v>
+        <v>8.527951167754564</v>
       </c>
       <c r="D17" t="n">
-        <v>46.50749371975173</v>
+        <v>7.557467729459656</v>
       </c>
       <c r="E17" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F17" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>43.21026973458127</v>
+        <v>7.021668831869457</v>
       </c>
       <c r="D18" t="n">
-        <v>36.43038974423924</v>
+        <v>5.919938333438876</v>
       </c>
       <c r="E18" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F18" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>25.67797572539019</v>
+        <v>4.172671055375907</v>
       </c>
       <c r="D19" t="n">
-        <v>17.51950763906028</v>
+        <v>2.846919991347295</v>
       </c>
       <c r="E19" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F19" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>37.27385430936025</v>
+        <v>6.05700132527104</v>
       </c>
       <c r="D20" t="n">
-        <v>28.37045945697829</v>
+        <v>4.610199661758973</v>
       </c>
       <c r="E20" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F20" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>17.34892089094481</v>
+        <v>2.819199644778533</v>
       </c>
       <c r="D21" t="n">
-        <v>14.68005020763415</v>
+        <v>2.385508158740549</v>
       </c>
       <c r="E21" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F21" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>18.80498210786136</v>
+        <v>3.055809592527471</v>
       </c>
       <c r="D22" t="n">
-        <v>23.64685416985228</v>
+        <v>3.842613802600995</v>
       </c>
       <c r="E22" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F22" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>13.50992326230151</v>
+        <v>2.195362530123996</v>
       </c>
       <c r="D23" t="n">
-        <v>18.78322035475958</v>
+        <v>3.052273307648432</v>
       </c>
       <c r="E23" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F23" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>6.222125685990974</v>
+        <v>1.011095423973533</v>
       </c>
       <c r="D24" t="n">
-        <v>6.08123705499584</v>
+        <v>0.988201021436824</v>
       </c>
       <c r="E24" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F24" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>19.3534256101903</v>
+        <v>3.144931661655924</v>
       </c>
       <c r="D25" t="n">
-        <v>20.90228052577906</v>
+        <v>3.396620585439097</v>
       </c>
       <c r="E25" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F25" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>38.46492329792522</v>
+        <v>6.250550035912849</v>
       </c>
       <c r="D26" t="n">
-        <v>30.21551265546251</v>
+        <v>4.910020806512658</v>
       </c>
       <c r="E26" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F26" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>21.44903127256357</v>
+        <v>3.485467581791581</v>
       </c>
       <c r="D27" t="n">
-        <v>19.13179099094568</v>
+        <v>3.108916036028673</v>
       </c>
       <c r="E27" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F27" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>23.00824157562938</v>
+        <v>3.738839256039775</v>
       </c>
       <c r="D28" t="n">
-        <v>27.47952518744076</v>
+        <v>4.465422842959124</v>
       </c>
       <c r="E28" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F28" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>28.95633961422544</v>
+        <v>4.705405187311634</v>
       </c>
       <c r="D29" t="n">
-        <v>27.93421566713966</v>
+        <v>4.539310045910196</v>
       </c>
       <c r="E29" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F29" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>30.45495416351467</v>
+        <v>4.948930051571134</v>
       </c>
       <c r="D30" t="n">
-        <v>28.42780229751474</v>
+        <v>4.619517873346146</v>
       </c>
       <c r="E30" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F30" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>37.07471611589182</v>
+        <v>6.024641368832421</v>
       </c>
       <c r="D31" t="n">
-        <v>37.97263844994813</v>
+        <v>6.170553748116571</v>
       </c>
       <c r="E31" t="n">
-        <v>11.41236077506994</v>
+        <v>1.854508625948865</v>
       </c>
       <c r="F31" t="n">
-        <v>9.707209381776499</v>
+        <v>1.577421524538681</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
